--- a/Result/checksun_type/網路卡.xlsx
+++ b/Result/checksun_type/網路卡.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>127.5</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>130.2</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>135.62</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>130.2</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>135.62</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>79964.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>94407.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>94407.39999999999</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>91269.6</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>207737.7</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>207737.7</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-16787.68714493714</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>79964</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>79964.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>125.5</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>130.43</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>135.91</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>130.43</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>135.91</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>98606.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>94759.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>94759.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>99059.1</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>221528.96</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>221528.96</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-16737.5513580027</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>98606</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>98606.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>124.0</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>130.57</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>136.32</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>130.57</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>136.32</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>61001.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>98412.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>98412.60000000001</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>120246.3</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>232237.94</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>232237.94</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-18065.51625673911</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>61001</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>61001.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>124.4</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>136.86</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>131</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>136.86</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>112462.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>100397.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>100397.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>147101.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>246240.56</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>246240.56</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-15288.3048171933</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>112462</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>112462.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>124.6</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>131.57</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>137.37</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>131.57</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>137.37</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>120004.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>95199.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>95199</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>159878.1</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>258672.3</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>258672.3</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-16288.52758865671</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>120004</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>120004.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>125.3</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>132.12</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>137.82</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>132.12</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>137.82</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>81726.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>88131.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>88131.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>160897.0</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>276222.6</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>276222.6</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-17943.75556258095</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>81726</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>81726.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>127.1</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>132.65</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>138.22</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>132.65</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>138.22</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>116870.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>103358.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>103358.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>167750.0</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>306194.04</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>306194.04</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-15566.30425523766</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>116870</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>116870.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>127.7</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>133.05</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>138.55</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>133.05</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>138.55</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>70926.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>142080.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>142080</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>172461.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>332412.34</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>332412.34</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-15379.43437848878</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>70926</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>70926.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>128.8</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>133.22</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>138.53</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>133.22</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>138.53</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>86469.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>193806.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>193806</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>178972.6</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>340328.8</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>340328.8</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-9640.640469615755</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>86469</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>86469.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>131.0</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>133.5</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>138.43</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>138.43</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>84668.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>224557.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>224557.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>177976.4</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>352282.84</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>352282.84</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-2763.376297310897</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>84668</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>84668.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>131.9</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>133.6</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>138.27</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>133.6</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>138.27</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>157859.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>233662.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>233662.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>179169.0</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>356682.06</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>356682.06</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>7352.943102314282</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>157859</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>157859.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>54.66</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>53.32</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>49.41</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>49.41</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>149413.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>217717.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>217717</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>367044.8</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>237158.66</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>237158.66</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-21084.67091178865</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>149413</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>149413.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>56.04</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>52.92</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>49.09</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>49.09</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>216732.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>231160.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>231160.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>420206.6</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>235339.22</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>235339.22</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-10587.49947517022</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>216732</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>216732.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>57.18000000000001</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>52.64</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>48.75</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>221658.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>259217.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>259217.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>453682.5</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>233052.36</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>233052.36</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-2426.165298745036</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>221658</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>221658.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>58.98</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>52.53</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>48.48</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>52.53</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>48.48</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>301588.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>336883.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>336883.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>450728.0</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>229641.16</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>229641.16</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>8791.746571103286</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>301588</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>301588.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>60.52</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>48.2</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>199194.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>396703.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>396703.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>425530.3</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>224069.9</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>224069.9</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>15939.41543620441</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>199194</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>199194.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>60.77999999999999</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>51.93</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>47.8</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>51.93</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>47.8</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>216632.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>516372.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>516372.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>418795.8</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>220937.42</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>220937.42</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>36551.8918350559</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>216632</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>216632.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>60.38</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>51.44</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>47.4</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>51.44</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>47.4</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>357016.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>609252.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>609252.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>418153.5</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>218290.42</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>218290.42</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>62824.50483930594</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>357016</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>357016.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>58.84</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>50.92</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>46.95</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>46.95</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>609988.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>648147.4</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>648147.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>393131.5</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>212611.62</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>212611.62</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>83071.93395825941</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>609988</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>609988.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>55.94</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>50.29</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>46.43</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>46.43</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>600689.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>564572.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>564572.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>357656.0</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>201223.44</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>201223.44</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>81925.83505825518</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>600689</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>600689.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>53.16</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>49.91</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>45.95</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>45.95</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>797538.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>454356.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>454356.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>315081.5</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>191580.74</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>191580.74</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>78358.94966331136</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>797538</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>797538.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>50.62</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>45.52</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>45.52</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>681031.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>321219.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>321219</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>255754.6</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>176809.8</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>176809.8</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>49373.9008968448</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>681031</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>681031.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>85.97999999999999</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>89.87</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>95.2</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>89.87</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>95.2</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>11375.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>7178.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>7178</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>8374.0</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>13947.82</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>13947.82</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-585.0773092036461</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>11375</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>11375.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>85.44000000000001</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>90.36</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>95.37</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>90.36</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>95.37</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>6678.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>6058.8</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>6058.8</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>8154.8</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>14227.02</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>14227.02</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-1011.350274117645</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>6678</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>6678.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>85.78</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>91.02</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>95.62</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>91.02</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>95.62</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>3344.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>7338.2</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>7338.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>8012.3</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>14403.68</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>14403.68</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-1080.941999919158</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>3344</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>3344.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>86.44</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>91.78</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>95.9</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>91.78</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>95.90000000000001</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>8809.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>8286.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>8286</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>8693.7</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>14904.86</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>14904.86</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-784.5393939242058</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>8809</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>8809.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>87.44000000000001</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>92.51</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>96.23</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>92.51000000000001</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>96.23</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>5684.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>8940.8</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>8940.799999999999</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>8390.2</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>15322.38</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>15322.38</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-918.6235498626957</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>5684</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>5684.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>88.18</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>93.19</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>96.5</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>93.19</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>96.5</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>5779.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>9570.0</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>9570</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>8442.6</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>16104.88</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>16104.88</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-742.5429315654419</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>5779</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>5779.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>89.14</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>93.88</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>96.72</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>93.88</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>96.72</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>13075.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>10250.8</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>10250.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>8727.8</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>16326.68</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>16326.68</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-474.6583721563147</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>13075</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>13075.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>89.74</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>94.45</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>96.92</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>94.45</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>96.92</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>8083.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>8686.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>8686.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>9463.4</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>16246.62</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>16246.62</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-856.7283454234039</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>8083</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>8083.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>90.16000000000001</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>94.99</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>97.05</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>94.98999999999999</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>97.05</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>12083.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>9101.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>9101.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>9314.6</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>16272.52</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>16272.52</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-837.0880091826984</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>12083</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>12083.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>90.52000000000001</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>95.45</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>97.17</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>97.17</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>8830.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>7839.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>7839.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>9048.9</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>16275.18</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>16275.18</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-1207.705814225166</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>8830</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>8830.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>90.9</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>95.86</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>97.3</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>95.86</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>97.3</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>9183.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>7315.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>7315.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>9715.6</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>16371.8</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>16371.8</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-1345.491756634936</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>9183</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>9183.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>586.6</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>636.0</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>667.3</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>636</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>667.3</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>2251806679.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>2845492684.8</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>2845492684.8</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>3254023064.0</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>2250939639.92</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>2250939639.92</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>80988449.20909452</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>2251806679</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>2251806679.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>577.4</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>640.85</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>668.88</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>640.85</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>668.88</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>2303990317.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>2895931468.2</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>2895931468.2</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>3423927956.4</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>2313304958.2</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>2313304958.2</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>168000892.6023631</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>2303990317</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>2303990317.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>572.0</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>646.8</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>670.44</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>646.8</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>670.4400000000001</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>4282414081.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>3701315712.0</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>3701315712</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>3406103963.5</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>2315429027.54</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>2315429027.54</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>280713247.2140913</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>4282414081</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>4282414081.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>577.0</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>653.25</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>671.96</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>653.25</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>671.96</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>3277325446.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>3639148367.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>3639148367.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>3149911827.2</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>2279747515.3</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>2279747515.3</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>219731448.8303423</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>3277325446</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>3277325446.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>589.0</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>659.5</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>673.4</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>659.5</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>673.4</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>2111926901.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>3434438489.8</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>3434438489.8</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>3061336173.2</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>2234436035.54</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>2234436035.54</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>232455110.2881894</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>2111926901</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>2111926901.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>601.0</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>665.8</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>674.84</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>665.8</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>674.84</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>2504000596.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>3662553443.2</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>3662553443.2</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>3053660242.7</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>2215412102.28</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>2215412102.28</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>367193931.1105347</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>2504000596</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>2504000596.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>617.2</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>672.05</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>676.22</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>672.05</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>676.22</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>6330911536.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>3951924444.6</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>3951924444.6</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>3034497195.4</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>2193079344.64</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>2193079344.64</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>504555995.9956522</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>6330911536</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>6330911536.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>636.8</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>678.2</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>677.46</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>678.2</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>677.46</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>3971577357.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>3110892215.0</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>3110892215</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>2577610128.3</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>2089597881.18</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>2089597881.18</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>272741488.1174035</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>3971577357</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>3971577357.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>647.4</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>681.95</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>677.64</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>681.95</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>677.64</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>2253776059.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>2660675287.2</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>2660675287.2</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>2395309044.8</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>2031062259.28</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>2031062259.28</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>184622942.8942842</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>2253776059</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>2253776059.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>653.6</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>684.55</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>677.36</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>684.55</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>677.36</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>3252501668.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>2688233856.6</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>2688233856.6</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>2353124375.3</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>2012331643.46</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>2012331643.46</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>236195769.4007463</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>3252501668</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>3252501668.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>663.2</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>687.1</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>677.34</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>687.1</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>677.34</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>3950855603.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>2444767042.2</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>2444767042.2</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>2195634921.6</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>1973519631.2</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>1973519631.2</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>194429357.3956661</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>3950855603</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>3950855603.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
